--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>87542617</v>
       </c>
       <c r="B2" t="n">
-        <v>105123</v>
+        <v>107017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424046.0116751689</v>
+        <v>424046</v>
       </c>
       <c r="R2" t="n">
-        <v>6476017.370924125</v>
+        <v>6476017</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2010-06-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
         <v>97163380</v>
       </c>
       <c r="B3" t="n">
-        <v>96970</v>
+        <v>98748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424046.0116751689</v>
+        <v>424046</v>
       </c>
       <c r="R3" t="n">
-        <v>6476017.370924125</v>
+        <v>6476017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +859,9 @@
           <t>2010-06-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-06-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>87542617</v>
       </c>
       <c r="B2" t="n">
-        <v>107017</v>
+        <v>107018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87542617</v>
+        <v>97163380</v>
       </c>
       <c r="B2" t="n">
-        <v>107040</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220103</v>
+        <v>259</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Hartmansstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Carex hartmaniorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>A.Cajander</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gruvesäter, Vg</t>
+          <t>Gruvesäter km2-ruta, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -759,12 +754,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkanter, skog, f d äng</t>
+          <t>Öppen lucka, Berghällar, Bäck</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,43 +782,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97163380</v>
+        <v>87542617</v>
       </c>
       <c r="B3" t="n">
-        <v>98770</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>259</v>
+        <v>220103</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hartmansstarr</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hartmaniorum</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A.Cajander</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gruvesäter km2-ruta, Vg</t>
+          <t>Gruvesäter, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -870,13 +861,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Öppen lucka, Berghällar, Bäck</t>
+          <t>Vägkanter, skog, f d äng</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 4312-2023 artfynd.xlsx
+++ b/artfynd/A 4312-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97163380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,8 +895,17 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87542617</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>